--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104600_W16.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104600_W16.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.5115</v>
+        <v>9.7745</v>
       </c>
       <c r="E2" t="n">
-        <v>8.7234</v>
+        <v>8.339600000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7881</v>
+        <v>1.4349</v>
       </c>
       <c r="G2" t="n">
-        <v>6.9281</v>
+        <v>4.5768</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6535</v>
+        <v>2.1653</v>
       </c>
       <c r="I2" t="n">
-        <v>6.2746</v>
+        <v>2.4114</v>
       </c>
       <c r="J2" t="n">
-        <v>7.7901</v>
+        <v>4.5893</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2224</v>
+        <v>2.4821</v>
       </c>
       <c r="L2" t="n">
-        <v>6.5677</v>
+        <v>2.1072</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.862</v>
+        <v>-0.0125</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5689</v>
+        <v>-0.3168</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2931</v>
+        <v>0.3043</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2825</v>
+        <v>-0.3878</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1179</v>
+        <v>-0.0141</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1645</v>
+        <v>-0.3736</v>
       </c>
       <c r="V2" t="n">
-        <v>2.1853</v>
+        <v>4.9026</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1853</v>
+        <v>4.9026</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.4374</v>
+        <v>9.638</v>
       </c>
       <c r="E3" t="n">
-        <v>7.8416</v>
+        <v>8.687799999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5958</v>
+        <v>0.9502</v>
       </c>
       <c r="G3" t="n">
-        <v>4.5791</v>
+        <v>6.9341</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1615</v>
+        <v>0.6629</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4176</v>
+        <v>6.2711</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6153</v>
+        <v>7.7635</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4936</v>
+        <v>1.2098</v>
       </c>
       <c r="L3" t="n">
-        <v>2.1216</v>
+        <v>6.5537</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0362</v>
+        <v>-0.8295</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3321</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2959</v>
+        <v>-0.2826</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7392</v>
+        <v>-0.1579</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5565</v>
+        <v>-0.1165</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1827</v>
+        <v>-0.0414</v>
       </c>
       <c r="V3" t="n">
-        <v>4.917</v>
+        <v>2.1789</v>
       </c>
       <c r="W3" t="n">
-        <v>4.917</v>
+        <v>2.1789</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7.6655</v>
+        <v>7.5246</v>
       </c>
       <c r="E4" t="n">
-        <v>5.6056</v>
+        <v>5.4104</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0599</v>
+        <v>2.1142</v>
       </c>
       <c r="G4" t="n">
-        <v>6.5105</v>
+        <v>6.5014</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3665</v>
+        <v>0.3676</v>
       </c>
       <c r="I4" t="n">
-        <v>6.144</v>
+        <v>6.1338</v>
       </c>
       <c r="J4" t="n">
-        <v>6.5099</v>
+        <v>6.4837</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1314</v>
+        <v>0.1239</v>
       </c>
       <c r="L4" t="n">
-        <v>6.3785</v>
+        <v>6.3598</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.0176</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2351</v>
+        <v>0.2437</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4745</v>
+        <v>0.3404</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2299</v>
+        <v>0.0648</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2447</v>
+        <v>0.2755</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>T. FORREST</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.0934</v>
+        <v>5.1456</v>
       </c>
       <c r="E5" t="n">
-        <v>2.509</v>
+        <v>4.6321</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5844</v>
+        <v>0.5135</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0896</v>
+        <v>4.7309</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.3782</v>
+        <v>2.8408</v>
       </c>
       <c r="I5" t="n">
-        <v>3.4679</v>
+        <v>1.8901</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8189</v>
+        <v>4.7714</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.313</v>
+        <v>2.3959</v>
       </c>
       <c r="L5" t="n">
-        <v>3.1319</v>
+        <v>2.3755</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2707</v>
+        <v>-0.0405</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0653</v>
+        <v>0.4449</v>
       </c>
       <c r="O5" t="n">
-        <v>0.336</v>
+        <v>-0.4854</v>
       </c>
       <c r="P5" t="n">
-        <v>2.722</v>
+        <v>0.4553</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>2.722</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4425</v>
+        <v>-0.0406</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5293</v>
+        <v>-0.0907</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0868</v>
+        <v>0.0501</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3214</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. FORREST</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.7492</v>
+        <v>4.2684</v>
       </c>
       <c r="E6" t="n">
-        <v>4.4729</v>
+        <v>1.7316</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2763</v>
+        <v>2.5368</v>
       </c>
       <c r="G6" t="n">
-        <v>4.7422</v>
+        <v>2.1044</v>
       </c>
       <c r="H6" t="n">
-        <v>2.847</v>
+        <v>-1.365</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8951</v>
+        <v>3.4694</v>
       </c>
       <c r="J6" t="n">
-        <v>4.7926</v>
+        <v>1.7995</v>
       </c>
       <c r="K6" t="n">
-        <v>2.407</v>
+        <v>-1.3207</v>
       </c>
       <c r="L6" t="n">
-        <v>2.3856</v>
+        <v>3.1202</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0504</v>
+        <v>0.3049</v>
       </c>
       <c r="N6" t="n">
-        <v>0.44</v>
+        <v>-0.0442</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4904</v>
+        <v>0.3492</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>2.7316</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5878</v>
+        <v>2.7316</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4467</v>
+        <v>-0.4098</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2782</v>
+        <v>-0.2257</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1685</v>
+        <v>-0.1841</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.0814</v>
+        <v>3.3607</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4218</v>
+        <v>0.8234</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6597</v>
+        <v>2.5373</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4191</v>
+        <v>3.4289</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1314</v>
+        <v>-0.1239</v>
       </c>
       <c r="I7" t="n">
-        <v>3.5505</v>
+        <v>3.5528</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5248</v>
+        <v>3.5111</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3188</v>
+        <v>-0.3242</v>
       </c>
       <c r="L7" t="n">
-        <v>3.8436</v>
+        <v>3.8354</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1057</v>
+        <v>-0.0822</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1874</v>
+        <v>0.2003</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2931</v>
+        <v>-0.2826</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1769</v>
+        <v>0.0896</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8347</v>
+        <v>-0.4114</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6578000000000001</v>
+        <v>0.501</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>S. JOKSIMOVIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.7996</v>
+        <v>2.7994</v>
       </c>
       <c r="E8" t="n">
-        <v>1.7275</v>
+        <v>2.5207</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0721</v>
+        <v>0.2787</v>
       </c>
       <c r="G8" t="n">
-        <v>3.936</v>
+        <v>3.6184</v>
       </c>
       <c r="H8" t="n">
-        <v>1.9395</v>
+        <v>-1.2956</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9965</v>
+        <v>4.914</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9414</v>
+        <v>3.9612</v>
       </c>
       <c r="K8" t="n">
-        <v>1.6726</v>
+        <v>-0.6485</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2688</v>
+        <v>4.6097</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9946</v>
+        <v>-0.3428</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2669</v>
+        <v>-0.6471</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7277</v>
+        <v>0.3043</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5878</v>
+        <v>2.0487</v>
       </c>
       <c r="S8" t="n">
-        <v>0.09039999999999999</v>
+        <v>-0.7978</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5081</v>
+        <v>-0.4601</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4177</v>
+        <v>-0.3377</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5463</v>
+        <v>-0.9317</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5463</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. JOKSIMOVIC</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.3391</v>
+        <v>2.6569</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2483</v>
+        <v>1.5361</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0907</v>
+        <v>1.1208</v>
       </c>
       <c r="G9" t="n">
-        <v>3.6203</v>
+        <v>3.9297</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3002</v>
+        <v>1.9305</v>
       </c>
       <c r="I9" t="n">
-        <v>4.9205</v>
+        <v>1.9992</v>
       </c>
       <c r="J9" t="n">
-        <v>3.987</v>
+        <v>2.924</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6375999999999999</v>
+        <v>1.658</v>
       </c>
       <c r="L9" t="n">
-        <v>4.6246</v>
+        <v>1.2661</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3666</v>
+        <v>1.0057</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6626</v>
+        <v>0.2725</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2959</v>
+        <v>0.7331</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9073</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0415</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2567</v>
+        <v>-0.0452</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7652</v>
+        <v>0.3436</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4915</v>
+        <v>-0.3888</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.5447</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1607</v>
+        <v>0.5447</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.9625</v>
+        <v>2.349</v>
       </c>
       <c r="E10" t="n">
-        <v>1.8311</v>
+        <v>2.338</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1315</v>
+        <v>0.0111</v>
       </c>
       <c r="G10" t="n">
-        <v>3.457</v>
+        <v>3.4597</v>
       </c>
       <c r="H10" t="n">
-        <v>1.29</v>
+        <v>1.2923</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1671</v>
+        <v>2.1674</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1787</v>
+        <v>3.1564</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4648</v>
+        <v>1.4511</v>
       </c>
       <c r="L10" t="n">
-        <v>1.7139</v>
+        <v>1.7052</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2784</v>
+        <v>0.3033</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1749</v>
+        <v>-0.1588</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-0.4749</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6956</v>
+        <v>-0.1535</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1618</v>
+        <v>-0.3213</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.3176</v>
+        <v>-1.3187</v>
       </c>
       <c r="W10" t="n">
-        <v>0.4822</v>
+        <v>0.4733</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1576</v>
+        <v>0.4789</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2652</v>
+        <v>0.7785</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4228</v>
+        <v>-0.2996</v>
       </c>
       <c r="G11" t="n">
-        <v>2.7348</v>
+        <v>2.73</v>
       </c>
       <c r="H11" t="n">
-        <v>0.909</v>
+        <v>0.9131</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8258</v>
+        <v>1.8169</v>
       </c>
       <c r="J11" t="n">
-        <v>3.3365</v>
+        <v>3.3165</v>
       </c>
       <c r="K11" t="n">
-        <v>1.1775</v>
+        <v>1.1721</v>
       </c>
       <c r="L11" t="n">
-        <v>2.159</v>
+        <v>2.1444</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6017</v>
+        <v>-0.5865</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2685</v>
+        <v>-0.259</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3215</v>
+        <v>0.3148</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4174</v>
+        <v>0.1253</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0959</v>
+        <v>0.1895</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.571</v>
+        <v>-2.5659</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0735</v>
+        <v>-1.8846</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2485</v>
+        <v>-0.5352</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.322</v>
+        <v>-1.3494</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2048</v>
+        <v>0.1991</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2004</v>
+        <v>-0.2092</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4052</v>
+        <v>0.4083</v>
       </c>
       <c r="J12" t="n">
-        <v>0.436</v>
+        <v>0.4104</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4196</v>
+        <v>-0.4384</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8556</v>
+        <v>0.8488</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2312</v>
+        <v>-0.2113</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2192</v>
+        <v>0.2292</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3193</v>
+        <v>0.5018</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9467</v>
+        <v>0.1925</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3726</v>
+        <v>0.3093</v>
       </c>
       <c r="V12" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>45.4085</v>
+        <v>46.1114</v>
       </c>
       <c r="E13" t="n">
-        <v>35.8949</v>
+        <v>36.263</v>
       </c>
       <c r="F13" t="n">
-        <v>9.5137</v>
+        <v>9.848500000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>42.2215</v>
+        <v>42.2134</v>
       </c>
       <c r="H13" t="n">
-        <v>7.1568</v>
+        <v>7.1788</v>
       </c>
       <c r="I13" t="n">
-        <v>35.0648</v>
+        <v>35.03439999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>42.9312</v>
+        <v>42.68699999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>7.880300000000001</v>
+        <v>7.761100000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>35.0508</v>
+        <v>34.926</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.7094999999999999</v>
+        <v>-0.4737999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7237</v>
+        <v>-0.5822000000000002</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01409999999999995</v>
+        <v>0.1084999999999998</v>
       </c>
       <c r="P13" t="n">
-        <v>6.805000000000001</v>
+        <v>6.829</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.7443</v>
+        <v>-14.7963</v>
       </c>
       <c r="R13" t="n">
-        <v>21.5492</v>
+        <v>21.6252</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.7542</v>
+        <v>-1.0674</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.4515</v>
+        <v>-0.7458000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3024999999999999</v>
+        <v>-0.3214999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.864000000000001</v>
+        <v>-1.8635</v>
       </c>
       <c r="W13" t="n">
-        <v>9.1593</v>
+        <v>9.117599999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-11.0232</v>
+        <v>-10.9811</v>
       </c>
     </row>
     <row r="14">
@@ -1501,55 +1501,55 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2283</v>
+        <v>0.3489</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0522</v>
+        <v>0.066</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2805</v>
+        <v>0.2829</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1559</v>
+        <v>-0.1551</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1559</v>
+        <v>-0.1551</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0696</v>
+        <v>0.0487</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0696</v>
+        <v>0.0487</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.431</v>
+        <v>-0.6526</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1285</v>
+        <v>2.9662</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.5595</v>
+        <v>-3.6188</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.0486</v>
+        <v>-2.0498</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4187</v>
+        <v>2.402</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.4673</v>
+        <v>-4.4518</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2201</v>
+        <v>3.1919</v>
       </c>
       <c r="K15" t="n">
-        <v>3.0335</v>
+        <v>3.0057</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.2688</v>
+        <v>-5.2417</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O15" t="n">
-        <v>-4.6539</v>
+        <v>-4.638</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3396</v>
+        <v>0.1288</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1693</v>
+        <v>-0.2861</v>
       </c>
       <c r="U15" t="n">
-        <v>0.509</v>
+        <v>0.4149</v>
       </c>
       <c r="V15" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. AKOBUNDU</t>
+          <t>L. SANCHEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.913</v>
+        <v>-0.9736</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1766</v>
+        <v>-0.7779</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.0896</v>
+        <v>-0.1957</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.5971</v>
+        <v>-1.5462</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.2857</v>
+        <v>-0.3932</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.3114</v>
+        <v>-1.153</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4568</v>
+        <v>-0.6872</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2149</v>
+        <v>-0.4934</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6717</v>
+        <v>-0.1939</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.0539</v>
+        <v>-0.859</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0708</v>
+        <v>0.1002</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.9831</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S16" t="n">
-        <v>1.325</v>
+        <v>-0.1103</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1735</v>
+        <v>-0.0907</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1515</v>
+        <v>-0.0196</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. SANCHEZ</t>
+          <t>K. AKOBUNDU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0554</v>
+        <v>-1.6325</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8797</v>
+        <v>1.4631</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1757</v>
+        <v>-3.0955</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.5396</v>
+        <v>-2.5885</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3881</v>
+        <v>-1.2839</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1515</v>
+        <v>-1.3046</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6711</v>
+        <v>0.4494</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4818</v>
+        <v>-0.2208</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1893</v>
+        <v>0.6703</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8685</v>
+        <v>-3.038</v>
       </c>
       <c r="N17" t="n">
-        <v>0.09370000000000001</v>
+        <v>-1.0631</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9622000000000001</v>
+        <v>-1.9749</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1963</v>
+        <v>0.5887</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2087</v>
+        <v>0.4689</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0124</v>
+        <v>0.1198</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. OLINDE</t>
+          <t>M. STEINBERGS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4101</v>
+        <v>-2.8794</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8453</v>
+        <v>1.0094</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.2554</v>
+        <v>-3.8888</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.8474</v>
+        <v>-4.4406</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5368000000000001</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.3106</v>
+        <v>-4.9512</v>
       </c>
       <c r="J18" t="n">
-        <v>0.035</v>
+        <v>0.6865</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0315</v>
+        <v>0.9997</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0665</v>
+        <v>-0.3132</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.8824</v>
+        <v>-5.1271</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5053</v>
+        <v>-0.4891</v>
       </c>
       <c r="O18" t="n">
-        <v>-3.3771</v>
+        <v>-4.638</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5878</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.4025</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8147</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>2.9325</v>
+        <v>-0.7967</v>
       </c>
       <c r="T18" t="n">
-        <v>3.0275</v>
+        <v>-0.6692</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.095</v>
+        <v>-0.1275</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0927</v>
+        <v>3.2684</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1853</v>
+        <v>3.2684</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. STEINBERGS</t>
+          <t>L. OLINDE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.4309</v>
+        <v>-3.1745</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8058</v>
+        <v>-0.0823</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.2367</v>
+        <v>-3.0922</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.4587</v>
+        <v>-3.8458</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4991</v>
+        <v>-0.5343</v>
       </c>
       <c r="I19" t="n">
-        <v>-4.9578</v>
+        <v>-3.3115</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7004</v>
+        <v>0.0063</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0044</v>
+        <v>-0.0452</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3039</v>
+        <v>0.0515</v>
       </c>
       <c r="M19" t="n">
-        <v>-5.1592</v>
+        <v>-3.8521</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5053</v>
+        <v>-0.4891</v>
       </c>
       <c r="O19" t="n">
-        <v>-4.6539</v>
+        <v>-3.3629</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9073</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2683</v>
+        <v>-3.4145</v>
       </c>
       <c r="R19" t="n">
-        <v>1.361</v>
+        <v>1.8211</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3428</v>
+        <v>1.1752</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9043</v>
+        <v>1.1469</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4386</v>
+        <v>0.0283</v>
       </c>
       <c r="V19" t="n">
-        <v>3.278</v>
+        <v>1.0895</v>
       </c>
       <c r="W19" t="n">
-        <v>3.278</v>
+        <v>2.1789</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.4761</v>
+        <v>-4.5228</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4141</v>
+        <v>0.3977</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.8902</v>
+        <v>-4.9205</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.85</v>
+        <v>-4.8499</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4732</v>
+        <v>-0.4766</v>
       </c>
       <c r="I20" t="n">
-        <v>-4.3768</v>
+        <v>-4.3734</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8389</v>
+        <v>-0.8541</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0622</v>
+        <v>0.055</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.901</v>
+        <v>-0.909</v>
       </c>
       <c r="M20" t="n">
-        <v>-4.0112</v>
+        <v>-3.9959</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5354</v>
+        <v>-0.5315</v>
       </c>
       <c r="O20" t="n">
-        <v>-3.4758</v>
+        <v>-3.4643</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S20" t="n">
-        <v>0.291</v>
+        <v>0.2298</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1603</v>
+        <v>0.1623</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1306</v>
+        <v>0.0675</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. PAULICAP</t>
+          <t>G. KNUDSEN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.6389</v>
+        <v>-4.8769</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.5703</v>
+        <v>-0.7841</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0686</v>
+        <v>-4.0929</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.0399</v>
+        <v>-5.4792</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1687</v>
+        <v>-1.5886</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.8711</v>
+        <v>-3.8906</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.82</v>
+        <v>0.3245</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.1519</v>
       </c>
       <c r="L21" t="n">
-        <v>0.112</v>
+        <v>0.4764</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.2198</v>
+        <v>-5.8037</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2368</v>
+        <v>-1.4367</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.9831</v>
+        <v>-4.367</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.4952</v>
+        <v>0.9105</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4025</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>2.0487</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0569</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3478</v>
+        <v>-0.1282</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4047</v>
+        <v>0.2069</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1607</v>
+        <v>-0.387</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1607</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. KNUDSEN</t>
+          <t>P. PAULICAP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.7809</v>
+        <v>-5.5361</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5924</v>
+        <v>-4.2375</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.1886</v>
+        <v>-1.2987</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.4915</v>
+        <v>-3.0348</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.5946</v>
+        <v>-1.1716</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.8969</v>
+        <v>-1.8632</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3368</v>
+        <v>-0.8298</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1456</v>
+        <v>-0.9415</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4824</v>
+        <v>0.1117</v>
       </c>
       <c r="M22" t="n">
-        <v>-5.8283</v>
+        <v>-2.205</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4489</v>
+        <v>-0.2301</v>
       </c>
       <c r="O22" t="n">
-        <v>-4.3794</v>
+        <v>-1.9749</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9073</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0415</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8111</v>
+        <v>0.1604</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9557</v>
+        <v>0.0068</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1446</v>
+        <v>0.1535</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3856</v>
+        <v>-0.1578</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5463</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.7058</v>
+        <v>-6.6086</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1426</v>
+        <v>-4.4143</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5632</v>
+        <v>-2.1943</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.8076</v>
+        <v>-3.8128</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6406</v>
+        <v>-1.6454</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.1671</v>
+        <v>-2.1674</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1938</v>
+        <v>-1.2198</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.8525</v>
+        <v>-0.8693</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.3413</v>
+        <v>-0.3505</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.6139</v>
+        <v>-2.5931</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.788</v>
+        <v>-0.7761</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.8258</v>
+        <v>-1.8169</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1515</v>
+        <v>-0.043</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0907</v>
+        <v>-0.1443</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2423</v>
+        <v>0.1013</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.2392</v>
+        <v>-7.0371</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8181</v>
+        <v>-3.4014</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.4211</v>
+        <v>-3.6357</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.8606</v>
+        <v>-4.8792</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4863</v>
+        <v>-0.4854</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.3743</v>
+        <v>-4.3937</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6636</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1763</v>
+        <v>0.1616</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.8399</v>
+        <v>-0.8729</v>
       </c>
       <c r="M24" t="n">
-        <v>-4.1969</v>
+        <v>-4.1679</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6626</v>
+        <v>-0.6471</v>
       </c>
       <c r="O24" t="n">
-        <v>-3.5344</v>
+        <v>-3.5209</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6055</v>
+        <v>-0.3856</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8861</v>
+        <v>-0.4138</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2806</v>
+        <v>0.0283</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.555300000000001</v>
+        <v>-7.8692</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.8286</v>
+        <v>-2.0534</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.7267</v>
+        <v>-5.8158</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.5245</v>
+        <v>-5.5314</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.3446</v>
+        <v>-2.3573</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.1799</v>
+        <v>-3.1741</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1306</v>
+        <v>0.0999</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.9116</v>
+        <v>-0.9350000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>1.0422</v>
+        <v>1.035</v>
       </c>
       <c r="M25" t="n">
-        <v>-5.6551</v>
+        <v>-5.6313</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.433</v>
+        <v>-1.4223</v>
       </c>
       <c r="O25" t="n">
-        <v>-4.2221</v>
+        <v>-4.2091</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q25" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0139</v>
+        <v>0.6897</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6079</v>
+        <v>0.2203</v>
       </c>
       <c r="U25" t="n">
-        <v>0.594</v>
+        <v>0.4694</v>
       </c>
       <c r="V25" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W25" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-45.4083</v>
+        <v>-45.4144</v>
       </c>
       <c r="E26" t="n">
-        <v>-9.513599999999999</v>
+        <v>-9.8485</v>
       </c>
       <c r="F26" t="n">
-        <v>-35.8948</v>
+        <v>-35.566</v>
       </c>
       <c r="G26" t="n">
-        <v>-42.2214</v>
+        <v>-42.2133</v>
       </c>
       <c r="H26" t="n">
-        <v>-7.1567</v>
+        <v>-7.178800000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-35.0647</v>
+        <v>-35.0345</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7096</v>
+        <v>0.4735999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.7238000000000002</v>
+        <v>0.5821000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.01400000000000001</v>
+        <v>-0.1084000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>-42.9312</v>
+        <v>-42.6872</v>
       </c>
       <c r="N26" t="n">
-        <v>-7.880500000000001</v>
+        <v>-7.760999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>-35.0508</v>
+        <v>-34.92610000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>-6.805</v>
+        <v>-6.828899999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>-21.5491</v>
+        <v>-21.625</v>
       </c>
       <c r="R26" t="n">
-        <v>14.7442</v>
+        <v>14.7962</v>
       </c>
       <c r="S26" t="n">
-        <v>1.7543</v>
+        <v>1.7644</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3026</v>
+        <v>0.3216</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4515</v>
+        <v>1.4428</v>
       </c>
       <c r="V26" t="n">
-        <v>1.8639</v>
+        <v>1.8634</v>
       </c>
       <c r="W26" t="n">
-        <v>11.0232</v>
+        <v>10.981</v>
       </c>
       <c r="X26" t="n">
-        <v>-9.1593</v>
+        <v>-9.117800000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104600_W16.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104600_W16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104600_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104600_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104600_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104600_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104600_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104600_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104600_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104600_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104600_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104600_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104600_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-10.9811</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104600_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104600_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104600_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104600_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104600_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104600_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104600_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104600_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104600_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104600_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104600_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104600_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-9.117800000000001</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
